--- a/src/16 Scientific Libraries/05 Spreadsheets/data/computing.xlsx
+++ b/src/16 Scientific Libraries/05 Spreadsheets/data/computing.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +506,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>1870</v>
       </c>
     </row>
